--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.37774540284745</v>
+        <v>6.88638362796271</v>
       </c>
       <c r="D2" t="n">
-        <v>41.92782674961072</v>
+        <v>6.813271846811742</v>
       </c>
       <c r="E2" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F2" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.3875452198808</v>
+        <v>8.02547609823063</v>
       </c>
       <c r="D3" t="n">
-        <v>48.76739055535236</v>
+        <v>7.924700965244759</v>
       </c>
       <c r="E3" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F3" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.97994170762442</v>
+        <v>6.821740527488968</v>
       </c>
       <c r="D4" t="n">
-        <v>42.00943569304341</v>
+        <v>6.826533300119555</v>
       </c>
       <c r="E4" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F4" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.65846808860802</v>
+        <v>4.982001064398804</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48497648754889</v>
+        <v>4.953808679226695</v>
       </c>
       <c r="E5" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F5" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.91465550848221</v>
+        <v>7.623631520128359</v>
       </c>
       <c r="D6" t="n">
-        <v>46.28495945105351</v>
+        <v>7.521305910796196</v>
       </c>
       <c r="E6" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F6" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.38341867570211</v>
+        <v>7.699805534801593</v>
       </c>
       <c r="D7" t="n">
-        <v>46.78789419703602</v>
+        <v>7.603032807018354</v>
       </c>
       <c r="E7" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F7" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.84253826081239</v>
+        <v>1.924412467382013</v>
       </c>
       <c r="D8" t="n">
-        <v>11.23315380881702</v>
+        <v>1.825387493932766</v>
       </c>
       <c r="E8" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F8" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.54250407501861</v>
+        <v>1.875656912190524</v>
       </c>
       <c r="D9" t="n">
-        <v>11.57731513649368</v>
+        <v>1.881313709680223</v>
       </c>
       <c r="E9" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F9" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.36531068758461</v>
+        <v>7.534362986732499</v>
       </c>
       <c r="D10" t="n">
-        <v>45.87663541537766</v>
+        <v>7.45495325499887</v>
       </c>
       <c r="E10" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F10" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.64385305362858</v>
+        <v>7.579626121214644</v>
       </c>
       <c r="D11" t="n">
-        <v>47.12469055592015</v>
+        <v>7.657762215337026</v>
       </c>
       <c r="E11" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F11" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.25409345658723</v>
+        <v>7.191290186695425</v>
       </c>
       <c r="D12" t="n">
-        <v>43.86276805191428</v>
+        <v>7.127699808436071</v>
       </c>
       <c r="E12" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F12" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.34486887563679</v>
+        <v>7.043541192290979</v>
       </c>
       <c r="D13" t="n">
-        <v>43.17529427625583</v>
+        <v>7.015985319891573</v>
       </c>
       <c r="E13" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F13" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.16694798768776</v>
+        <v>6.039629047999262</v>
       </c>
       <c r="D14" t="n">
-        <v>37.79244447635173</v>
+        <v>6.141272227407156</v>
       </c>
       <c r="E14" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F14" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.24738697707028</v>
+        <v>6.052700383773922</v>
       </c>
       <c r="D15" t="n">
-        <v>37.74999774325807</v>
+        <v>6.134374633279437</v>
       </c>
       <c r="E15" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F15" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.28199062196398</v>
+        <v>6.708323476069148</v>
       </c>
       <c r="D16" t="n">
-        <v>41.83551540843568</v>
+        <v>6.798271253870798</v>
       </c>
       <c r="E16" t="n">
-        <v>11.51817102728152</v>
+        <v>1.871702791933248</v>
       </c>
       <c r="F16" t="n">
-        <v>11.49745253195211</v>
+        <v>1.868336036442218</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
